--- a/Toeic/part1/ReviewWords.xlsx
+++ b/Toeic/part1/ReviewWords.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EnglishLearnning3\Toeic\part1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F19DBC-4A86-486D-8B60-040CB472A6CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196D7ADB-F6D0-4355-84E1-AD759CA0F637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="1やり直し英語Eigo Chat Lab! TOEICとその一" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,17 +25,759 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
   <si>
     <t>word</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04 - 【写真描写100問集中トレーニング】TOEIC Part1 リスニング 聞き流し対応</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>check(ok)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>check(wrong)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>brushing</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tidying up
+decorating</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sealed</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>overlaping</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>stroll</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>stationery
+propped up</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>shelves</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rearrangeing
+assembling</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>flat tire</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>handrail ,cast on the ground</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>droopped</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>thing hung on the wall</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>awning
+shutter
+signboard</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dimensions</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>gripping</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bracelet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>keeeling</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>globe</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>broom</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tripod</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ovation,bouquet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>stirring</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>shrubs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>inflating a bollon,
+whistling</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>illuminates,hang over</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>coordinated</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rug</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>doorknob</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>strring</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>corner</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rinsing</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>brushing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 磨くこと、ブラシをかけること</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>tidying up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 片付け、整理整頓</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>decorating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 装飾、飾り付け</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sealed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 密閉された、封をされた</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>overlapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 重なり合っている</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>stroll</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 散策、ぶらぶら歩く</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>stationery</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 文房具</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>propped up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 立てかけられた</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>shelves</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 棚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>rearranging</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 並べ替え、模様替え</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>assembling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 組み立て</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>flat tire</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: パンク</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>handrail</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 手すり</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>cast on the ground</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 地面に投げ出された（または、地面に影を落としている）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>dropped</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 落ちた、下がった</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>thing hung on the wall</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 壁掛け、壁に掛かっているもの</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>awning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 日よけ、雨よけ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>shutter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: シャッター</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>signboard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 看板</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>dimensions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 寸法、サイズ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>gripping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: しっかり握っている</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>bracelet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: ブレスレット</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>kneeling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: ひざまずいている</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>globe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 地球儀</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>broom</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: ほうき</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>tripod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 三脚</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ovation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 拍手喝采</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>bouquet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 花束</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>stirring</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: かき混ぜること</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>shrubs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 低木、植木</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>inflating a balloon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 風船を膨らませている</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>whistling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 口笛を吹いている</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>illuminates</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 照らす、明るくする</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>hang over</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 覆いかぶさる、ぶら下がる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>coordinated</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 調和のとれた、コーディネートされた</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>rug</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: ラグ、敷物</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>doorknob</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: ドアノブ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 紐</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>corner</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: 角、隅</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>rinsing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: すすぐこと、洗い流す</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -56,6 +798,14 @@
       <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -84,10 +834,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -103,6 +869,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -368,17 +1151,1388 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="67.8984375" customWidth="1"/>
+    <col min="1" max="1" width="5.5" customWidth="1"/>
+    <col min="2" max="2" width="10.796875" customWidth="1"/>
+    <col min="3" max="3" width="14.796875" customWidth="1"/>
+    <col min="4" max="4" width="66.19921875" customWidth="1"/>
+    <col min="5" max="5" width="44.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1">
+    <row r="1" spans="1:5" s="2" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="36">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:5" ht="36">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="36">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30" spans="1:5" ht="54">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C32" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C36" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C37" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="5"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C38" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C39" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C44" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C45" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="5"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C46" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C48" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="5"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C50" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="5"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C52" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" s="5"/>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C54" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" s="5"/>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C56" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D56" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" s="5"/>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C58" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C59" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" s="5"/>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D60" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C61" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C62" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D62" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C63" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D63" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" s="5"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C64" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C65" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" s="5"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C66" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="36">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C67" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67" s="5"/>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C68" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C69" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" s="5"/>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C70" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C71" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" s="5"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C72" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C73" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" s="5"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C75" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" s="5"/>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C76" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C77" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" s="5"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C78" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C79" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D79" t="s">
+        <v>28</v>
+      </c>
+      <c r="E79" s="5"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C80" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C81" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C82" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C83" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C84" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D84" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C85" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C86" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C87" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D87" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C88" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C89" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C90" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C91" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C92" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C93" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D93" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C94" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D94" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C95" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C96" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C97" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C98" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D98" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C99" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D99" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="B100" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C100" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="B101" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C101" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="B102" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="C102" s="3" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
